--- a/results/BMW_2022_indicators.xlsx
+++ b/results/BMW_2022_indicators.xlsx
@@ -658,7 +658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RISK ASSESSMENT</t>
+          <t>RISK ASSESSMENT (10-POINT SCALE)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>High vague language (&gt;40%); Moderate quantification (15-25%)</t>
+          <t>Excessive vague language (&gt;40%); Minimal quantification (15-25%); Very low risk disclosure (&lt;5%)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
